--- a/Assets/c#/Dialog/mate.xlsx
+++ b/Assets/c#/Dialog/mate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/allen/Documents/GitHub/WhiteNight/Assets/c#/Dialog/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50AAAC62-BE09-9C45-B700-A2BF479AC55E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99BB3F9F-C0CD-B64D-932A-49629497C2E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -79,10 +79,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>seq_1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>你好</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -99,16 +95,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>seq_2</t>
-  </si>
-  <si>
-    <t>seq_3</t>
-  </si>
-  <si>
     <t>第二次对话</t>
   </si>
   <si>
     <t>第三次对话</t>
+  </si>
+  <si>
+    <t>1_seq_1</t>
+  </si>
+  <si>
+    <t>1_seq_2</t>
+  </si>
+  <si>
+    <t>1_seq_3</t>
   </si>
 </sst>
 </file>
@@ -473,10 +472,10 @@
         <v>7</v>
       </c>
       <c r="I1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1" t="s">
         <v>16</v>
-      </c>
-      <c r="J1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
@@ -493,7 +492,7 @@
         <v>5</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -502,7 +501,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -519,7 +518,7 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -528,7 +527,7 @@
         <v>1</v>
       </c>
       <c r="H3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
@@ -545,7 +544,7 @@
         <v>5</v>
       </c>
       <c r="E4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F4">
         <v>2</v>
@@ -554,7 +553,7 @@
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
@@ -571,7 +570,7 @@
         <v>5</v>
       </c>
       <c r="E5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F5">
         <v>2</v>
@@ -580,7 +579,7 @@
         <v>1</v>
       </c>
       <c r="H5" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
@@ -597,7 +596,7 @@
         <v>5</v>
       </c>
       <c r="E6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F6">
         <v>3</v>
@@ -606,7 +605,7 @@
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
@@ -623,7 +622,7 @@
         <v>5</v>
       </c>
       <c r="E7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F7">
         <v>3</v>
@@ -632,7 +631,7 @@
         <v>1</v>
       </c>
       <c r="H7" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
